--- a/data/trans_orig/P70D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de su capacidad laboral actual en 2023</t>
+          <t>Población según su autopercepción de su capacidad laboral actual en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43782</t>
+          <t>45372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>27384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49010</t>
+          <t>49956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50749</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85849</t>
+          <t>84703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45579</t>
+          <t>45205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26943</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>63795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42921</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24131</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59809</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>26923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111139</t>
+          <t>109834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158315</t>
+          <t>156191</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128901</t>
+          <t>129074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149076</t>
+          <t>161372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266310</t>
+          <t>269142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77307</t>
+          <t>78113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119728</t>
+          <t>121283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89353</t>
+          <t>91160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>244617</t>
+          <t>250166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186162</t>
+          <t>184179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400358</t>
+          <t>369903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58686</t>
+          <t>59703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100128</t>
+          <t>98608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115222</t>
+          <t>112218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>110495</t>
+          <t>118347</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195789</t>
+          <t>195267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49856</t>
+          <t>50728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24141</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67858</t>
+          <t>69457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2671,47 +2671,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>14238</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1573</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>12963</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162304</t>
+          <t>160427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204874</t>
+          <t>205366</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>103818</t>
+          <t>104143</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132299</t>
+          <t>134091</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>275612</t>
+          <t>273943</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>330915</t>
+          <t>328238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108254</t>
+          <t>107955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>149553</t>
+          <t>149562</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>68657</t>
+          <t>69280</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>94361</t>
+          <t>93981</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>185105</t>
+          <t>184867</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>233393</t>
+          <t>232993</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94767</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131267</t>
+          <t>132315</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3641,47 +3641,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>113221</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>99549</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>128061</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>32,24%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>28,34%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>113221</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>99071</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>127717</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>200590</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>250192</t>
+          <t>249929</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36938</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39932</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>65999</t>
+          <t>64432</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24054</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>69243</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>278928</t>
+          <t>279576</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>116335</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>223233</t>
+          <t>230006</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>172091</t>
+          <t>175557</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>424442</t>
+          <t>428906</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>184227</t>
+          <t>187044</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>598312</t>
+          <t>594038</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>95770</t>
+          <t>94999</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>140613</t>
+          <t>141310</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>310078</t>
+          <t>308179</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>823845</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>56081</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>221949</t>
+          <t>219797</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>98164</t>
+          <t>96461</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>148256</t>
+          <t>149426</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>139990</t>
+          <t>140339</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>351896</t>
+          <t>352474</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>41607</t>
+          <t>40769</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>35168</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>70213</t>
+          <t>69922</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>32159</t>
+          <t>32115</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42996</t>
+          <t>42804</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>38785</t>
+          <t>36685</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>403</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>71729</t>
+          <t>71792</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>102798</t>
+          <t>101142</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>49342</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>67958</t>
+          <t>68185</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>128799</t>
+          <t>129564</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>165605</t>
+          <t>163183</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>60678</t>
+          <t>61064</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>90618</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38940</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>105621</t>
+          <t>106376</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>139350</t>
+          <t>139846</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>76440</t>
+          <t>77074</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>107032</t>
+          <t>107546</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48883</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>67520</t>
+          <t>67262</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>133389</t>
+          <t>132041</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>168987</t>
+          <t>166959</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>13434</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>28799</t>
+          <t>29669</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>32499</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>52755</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>31334</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>499</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7418,12 +7418,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8417,12 +8417,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8528,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9533,12 +9533,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>429231</t>
+          <t>374173</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>720694</t>
+          <t>723172</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>396944</t>
+          <t>401919</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>538004</t>
+          <t>533742</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>846002</t>
+          <t>829683</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>1199173</t>
+          <t>1195316</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>516881</t>
+          <t>513755</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1101042</t>
+          <t>1214383</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>348449</t>
+          <t>352638</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>582346</t>
+          <t>574774</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>905732</t>
+          <t>909197</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>1687297</t>
+          <t>1656796</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -10316,12 +10316,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>301033</t>
+          <t>265738</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>530830</t>
+          <t>533171</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>341864</t>
+          <t>348749</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>443784</t>
+          <t>447533</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10386,12 +10386,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>663246</t>
+          <t>676970</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>959748</t>
+          <t>955252</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -10427,12 +10427,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>139277</t>
+          <t>141579</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>78721</t>
+          <t>79634</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>117285</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>162013</t>
+          <t>158828</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>245015</t>
+          <t>244146</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -10538,12 +10538,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>67635</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10553,49 +10553,49 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>35983</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>26655</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>48219</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>35983</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>25995</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>48662</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="P92" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -10608,12 +10608,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>64067</t>
+          <t>63569</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>106637</t>
+          <t>108241</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10719,12 +10719,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -10760,12 +10760,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -10871,12 +10871,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -10982,12 +10982,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11067,12 +11067,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11289,12 +11289,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Edad-trans_orig.xlsx
@@ -723,32 +723,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>39919</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45372</t>
+          <t>57569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49956</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>67313</t>
+          <t>79940</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>60123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84703</t>
+          <t>100112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -834,32 +834,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45205</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43650</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>62651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -945,32 +945,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45333</t>
+          <t>46752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,32 +980,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>68578</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -1202,32 +1202,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>131977</t>
+          <t>148993</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109834</t>
+          <t>123588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156191</t>
+          <t>174752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97950</t>
+          <t>109375</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53668</t>
+          <t>93495</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129074</t>
+          <t>128938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>229926</t>
+          <t>258369</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161372</t>
+          <t>228135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269142</t>
+          <t>291327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -2172,32 +2172,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98504</t>
+          <t>109818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78113</t>
+          <t>88584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121283</t>
+          <t>136092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2207,32 +2207,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>146891</t>
+          <t>83853</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>68758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250166</t>
+          <t>102143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>245394</t>
+          <t>193671</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184179</t>
+          <t>167368</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369903</t>
+          <t>221470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -2283,32 +2283,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77623</t>
+          <t>84476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>64494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>106398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2318,32 +2318,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38774</t>
+          <t>82824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112218</t>
+          <t>116873</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2353,32 +2353,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162575</t>
+          <t>183702</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118347</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195267</t>
+          <t>213906</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -2394,32 +2394,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>40677</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>62784</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2429,32 +2429,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2464,32 +2464,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>45912</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29612</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69457</t>
+          <t>77474</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2505,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2540,32 +2540,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2575,32 +2575,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2651,32 +2651,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2686,27 +2686,27 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>394617</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>394617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>394617</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>702059</t>
+          <t>713822</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>702059</t>
+          <t>713822</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>702059</t>
+          <t>713822</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3399,32 +3399,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>183062</t>
+          <t>212359</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160427</t>
+          <t>190056</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205366</t>
+          <t>239391</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>118398</t>
+          <t>132424</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>104143</t>
+          <t>116646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134091</t>
+          <t>148970</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>301460</t>
+          <t>344783</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>273943</t>
+          <t>315382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>328238</t>
+          <t>375338</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>127094</t>
+          <t>146824</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107955</t>
+          <t>123886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>149562</t>
+          <t>170028</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3545,32 +3545,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>80810</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69280</t>
+          <t>77668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93981</t>
+          <t>107209</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3580,32 +3580,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>207903</t>
+          <t>239053</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>184867</t>
+          <t>215205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>232993</t>
+          <t>265454</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -3621,32 +3621,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>112458</t>
+          <t>131661</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>109129</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>132315</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113221</t>
+          <t>130557</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>99549</t>
+          <t>115054</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128061</t>
+          <t>148231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3691,32 +3691,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>225680</t>
+          <t>262218</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>201857</t>
+          <t>235265</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>249929</t>
+          <t>289862</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -3732,32 +3732,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3767,32 +3767,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>27417</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33707</t>
+          <t>36977</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3802,32 +3802,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>60948</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64432</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3843,32 +3843,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3913,32 +3913,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3989,67 +3989,67 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2332</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>10667</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>4464</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>9178</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>870</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4519,92 +4519,92 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3832</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1671</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>1660</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>5197</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>463168</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>463168</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>463168</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4657,17 +4657,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>351210</t>
+          <t>397591</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>351210</t>
+          <t>397591</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>351210</t>
+          <t>397591</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>814378</t>
+          <t>937049</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>814378</t>
+          <t>937049</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>814378</t>
+          <t>937049</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>178449</t>
+          <t>190442</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>168685</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>279576</t>
+          <t>213372</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4772,32 +4772,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>145277</t>
+          <t>125524</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>116377</t>
+          <t>111261</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>230006</t>
+          <t>142715</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4807,32 +4807,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>323727</t>
+          <t>315966</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>175557</t>
+          <t>287420</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>428906</t>
+          <t>342865</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>376145</t>
+          <t>148650</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>187044</t>
+          <t>129098</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>594038</t>
+          <t>171338</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>123248</t>
+          <t>133181</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>94999</t>
+          <t>118344</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>141310</t>
+          <t>149653</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>499393</t>
+          <t>281832</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>308179</t>
+          <t>255880</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>823845</t>
+          <t>308503</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4959,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>141349</t>
+          <t>151053</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>56260</t>
+          <t>130772</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>175561</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4994,32 +4994,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>140424</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>96461</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>149426</t>
+          <t>155916</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5029,32 +5029,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>271603</t>
+          <t>291477</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>140339</t>
+          <t>266569</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>352474</t>
+          <t>317022</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -5070,32 +5070,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>24827</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>35168</t>
+          <t>36477</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5140,32 +5140,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>50977</t>
+          <t>55326</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>69922</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5181,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>19407</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5216,32 +5216,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5251,32 +5251,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5292,32 +5292,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5362,32 +5362,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>811</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>645</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -5549,32 +5549,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5584,32 +5584,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5695,32 +5695,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>755</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>556</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5960,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>746527</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>746527</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>746527</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5995,17 +5995,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>453983</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>453983</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>453983</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1000192</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1000192</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1000192</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6075,32 +6075,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>87077</t>
+          <t>96620</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>71792</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>101142</t>
+          <t>111928</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6110,32 +6110,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>58625</t>
+          <t>66657</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>49342</t>
+          <t>55565</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>68185</t>
+          <t>78255</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>145702</t>
+          <t>163278</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>129564</t>
+          <t>143966</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>163183</t>
+          <t>183499</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -6186,32 +6186,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>73826</t>
+          <t>79401</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>61064</t>
+          <t>64979</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>95424</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6221,32 +6221,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>47250</t>
+          <t>51885</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>56734</t>
+          <t>61845</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6256,32 +6256,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>121075</t>
+          <t>131285</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>114581</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>139846</t>
+          <t>150823</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -6297,32 +6297,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>91789</t>
+          <t>99525</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>77074</t>
+          <t>83234</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>107546</t>
+          <t>113551</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6332,32 +6332,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>65516</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>55936</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>67262</t>
+          <t>76873</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6367,32 +6367,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>149763</t>
+          <t>165041</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>132041</t>
+          <t>146609</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>166959</t>
+          <t>185244</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -6408,102 +6408,102 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>29669</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>24547</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>18139</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>32626</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>48817</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>38453</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>61858</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>21251</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>15977</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>29105</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>41800</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>32940</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>52469</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -6519,32 +6519,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6554,32 +6554,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6589,32 +6589,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6630,32 +6630,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6665,32 +6665,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6700,32 +6700,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6741,32 +6741,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6776,32 +6776,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>514</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6922,32 +6922,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -6998,32 +6998,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7033,32 +7033,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>818</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7084,92 +7084,92 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>3146</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>1454</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>4711</t>
-        </is>
-      </c>
-      <c r="U61" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>327902</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>327902</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>327902</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>505690</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>505690</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>505690</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -7524,32 +7524,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7559,32 +7559,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7594,32 +7594,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -7635,32 +7635,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7670,32 +7670,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7705,32 +7705,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7816,32 +7816,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>732</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7927,32 +7927,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>890</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>890</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -8636,17 +8636,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9974,17 +9974,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>617434</t>
+          <t>696546</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>374173</t>
+          <t>649340</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>723172</t>
+          <t>745352</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>461122</t>
+          <t>477530</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>401919</t>
+          <t>445435</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>533742</t>
+          <t>512618</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10159,32 +10159,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>1078556</t>
+          <t>1174076</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>829683</t>
+          <t>1115583</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>1195316</t>
+          <t>1234637</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -10200,32 +10200,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>707585</t>
+          <t>515172</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>513755</t>
+          <t>474516</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1214383</t>
+          <t>558838</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>416076</t>
+          <t>381042</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>352638</t>
+          <t>352488</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>574774</t>
+          <t>409963</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10270,32 +10270,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>1123662</t>
+          <t>896215</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>909197</t>
+          <t>843995</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>1656796</t>
+          <t>954988</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -10311,32 +10311,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>455001</t>
+          <t>503228</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>265738</t>
+          <t>462067</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>533171</t>
+          <t>552410</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10346,32 +10346,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>405010</t>
+          <t>459564</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>348749</t>
+          <t>428191</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>447533</t>
+          <t>495089</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10381,32 +10381,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>860011</t>
+          <t>962792</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>676970</t>
+          <t>907123</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>955252</t>
+          <t>1015872</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -10422,32 +10422,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>110058</t>
+          <t>134548</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>141579</t>
+          <t>164383</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10457,32 +10457,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>97655</t>
+          <t>106840</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>79634</t>
+          <t>89216</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>117285</t>
+          <t>126154</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10492,32 +10492,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>207713</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>158828</t>
+          <t>212052</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>244146</t>
+          <t>271739</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -10533,32 +10533,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>40569</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>67635</t>
+          <t>72150</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10568,32 +10568,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>54106</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10603,32 +10603,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>84909</t>
+          <t>94702</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>76141</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>108241</t>
+          <t>117486</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -10644,32 +10644,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10679,32 +10679,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>40572</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10714,32 +10714,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>56342</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10755,32 +10755,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10790,67 +10790,67 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>11452</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>18737</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R94" s="2" t="inlineStr">
-        <is>
-          <t>11053</t>
-        </is>
-      </c>
-      <c r="S94" s="2" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="T94" s="2" t="inlineStr">
-        <is>
-          <t>18776</t>
-        </is>
-      </c>
-      <c r="U94" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V94" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -10866,32 +10866,32 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -10901,67 +10901,67 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>17599</t>
+        </is>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R95" s="2" t="inlineStr">
-        <is>
-          <t>9163</t>
-        </is>
-      </c>
-      <c r="S95" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="T95" s="2" t="inlineStr">
-        <is>
-          <t>15830</t>
-        </is>
-      </c>
-      <c r="U95" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V95" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -11012,17 +11012,17 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11032,39 +11032,39 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R96" s="2" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
-      </c>
-      <c r="S96" s="2" t="inlineStr">
-        <is>
-          <t>2264</t>
-        </is>
-      </c>
-      <c r="T96" s="2" t="inlineStr">
-        <is>
-          <t>9151</t>
-        </is>
-      </c>
-      <c r="U96" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -11088,17 +11088,17 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11123,17 +11123,17 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11178,12 +11178,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -11199,32 +11199,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11269,17 +11269,17 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11312,17 +11312,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11347,17 +11347,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11382,17 +11382,17 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
